--- a/test-data/logins.xlsx
+++ b/test-data/logins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce-playwright\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3296163-109F-4362-A556-963510992CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47438C6A-5B13-47EA-A12E-15DB9C82BF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,18 +25,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>varaprasad1819@gmail.com</t>
   </si>
   <si>
     <t>Prasu$1819</t>
+  </si>
+  <si>
+    <t>s.no</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>john.doegvv85@example.com</t>
+  </si>
+  <si>
+    <t>Password123</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Valid</t>
   </si>
 </sst>
 </file>
@@ -365,32 +389,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{AEA7F3DC-CB11-4CE5-9C71-E2217A02A490}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{E04FE6F9-69BC-48C9-8721-D96DC705DF94}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{2255E5ED-BC54-4059-BDC4-B6F6F118677E}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{7F49B8CE-B4E8-4B61-BD5F-DB965D0702FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
